--- a/excel-files/LAS PINAS/LAS PIÑAS CITY NATIONAL SENIOR HIGH SCHOOL - CAA CAMPUS.xlsx
+++ b/excel-files/LAS PINAS/LAS PIÑAS CITY NATIONAL SENIOR HIGH SCHOOL - CAA CAMPUS.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29711"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29816"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jonathan Buquia\Downloads\OFFICE\SEMINARS\Workshop on the Strengthened Regional Inventory of Learning Resources\SCHOOLS in NCR\CALOOCAN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{733ECEEF-EAF5-4B3B-AB6B-14E795138755}"/>
+  <xr:revisionPtr revIDLastSave="42" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E845155A-097E-4A52-A575-CFE79B2A3857}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -736,6 +736,12 @@
     <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -747,12 +753,6 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5385,38 +5385,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" s="28" customFormat="1" ht="34.15" customHeight="1">
-      <c r="D1" s="40" t="s">
+      <c r="D1" s="42" t="s">
         <v>32</v>
       </c>
-      <c r="E1" s="40"/>
-      <c r="F1" s="40"/>
-      <c r="G1" s="40"/>
-      <c r="H1" s="40"/>
-      <c r="I1" s="40"/>
-      <c r="J1" s="41" t="s">
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
+      <c r="G1" s="42"/>
+      <c r="H1" s="42"/>
+      <c r="I1" s="42"/>
+      <c r="J1" s="43" t="s">
         <v>33</v>
       </c>
-      <c r="K1" s="41"/>
-      <c r="L1" s="41"/>
-      <c r="M1" s="41"/>
-      <c r="N1" s="41"/>
-      <c r="O1" s="41"/>
-      <c r="P1" s="42" t="s">
+      <c r="K1" s="43"/>
+      <c r="L1" s="43"/>
+      <c r="M1" s="43"/>
+      <c r="N1" s="43"/>
+      <c r="O1" s="43"/>
+      <c r="P1" s="44" t="s">
         <v>34</v>
       </c>
-      <c r="Q1" s="42"/>
-      <c r="R1" s="42"/>
-      <c r="S1" s="42"/>
-      <c r="T1" s="42"/>
-      <c r="U1" s="42"/>
-      <c r="V1" s="43" t="s">
+      <c r="Q1" s="44"/>
+      <c r="R1" s="44"/>
+      <c r="S1" s="44"/>
+      <c r="T1" s="44"/>
+      <c r="U1" s="44"/>
+      <c r="V1" s="45" t="s">
         <v>35</v>
       </c>
-      <c r="W1" s="43"/>
-      <c r="X1" s="43"/>
-      <c r="Y1" s="43"/>
-      <c r="Z1" s="43"/>
-      <c r="AA1" s="43"/>
+      <c r="W1" s="45"/>
+      <c r="X1" s="45"/>
+      <c r="Y1" s="45"/>
+      <c r="Z1" s="45"/>
+      <c r="AA1" s="45"/>
     </row>
     <row r="2" spans="1:27" ht="69.599999999999994" customHeight="1">
       <c r="A2" s="15" t="s">
@@ -5455,10 +5455,10 @@
       <c r="L2" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="M2" s="44" t="s">
+      <c r="M2" s="40" t="s">
         <v>45</v>
       </c>
-      <c r="N2" s="44" t="s">
+      <c r="N2" s="40" t="s">
         <v>46</v>
       </c>
       <c r="O2" s="22" t="s">
@@ -5491,10 +5491,10 @@
       <c r="X2" s="27" t="s">
         <v>56</v>
       </c>
-      <c r="Y2" s="45" t="s">
+      <c r="Y2" s="41" t="s">
         <v>57</v>
       </c>
-      <c r="Z2" s="45" t="s">
+      <c r="Z2" s="41" t="s">
         <v>58</v>
       </c>
       <c r="AA2" s="26" t="s">
@@ -13589,38 +13589,38 @@
   <sheetData>
     <row r="1" spans="1:27" s="28" customFormat="1" ht="34.15" customHeight="1">
       <c r="B1" s="35"/>
-      <c r="D1" s="40" t="s">
+      <c r="D1" s="42" t="s">
         <v>32</v>
       </c>
-      <c r="E1" s="40"/>
-      <c r="F1" s="40"/>
-      <c r="G1" s="40"/>
-      <c r="H1" s="40"/>
-      <c r="I1" s="40"/>
-      <c r="J1" s="41" t="s">
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
+      <c r="G1" s="42"/>
+      <c r="H1" s="42"/>
+      <c r="I1" s="42"/>
+      <c r="J1" s="43" t="s">
         <v>33</v>
       </c>
-      <c r="K1" s="41"/>
-      <c r="L1" s="41"/>
-      <c r="M1" s="41"/>
-      <c r="N1" s="41"/>
-      <c r="O1" s="41"/>
-      <c r="P1" s="42" t="s">
+      <c r="K1" s="43"/>
+      <c r="L1" s="43"/>
+      <c r="M1" s="43"/>
+      <c r="N1" s="43"/>
+      <c r="O1" s="43"/>
+      <c r="P1" s="44" t="s">
         <v>34</v>
       </c>
-      <c r="Q1" s="42"/>
-      <c r="R1" s="42"/>
-      <c r="S1" s="42"/>
-      <c r="T1" s="42"/>
-      <c r="U1" s="42"/>
-      <c r="V1" s="43" t="s">
+      <c r="Q1" s="44"/>
+      <c r="R1" s="44"/>
+      <c r="S1" s="44"/>
+      <c r="T1" s="44"/>
+      <c r="U1" s="44"/>
+      <c r="V1" s="45" t="s">
         <v>35</v>
       </c>
-      <c r="W1" s="43"/>
-      <c r="X1" s="43"/>
-      <c r="Y1" s="43"/>
-      <c r="Z1" s="43"/>
-      <c r="AA1" s="43"/>
+      <c r="W1" s="45"/>
+      <c r="X1" s="45"/>
+      <c r="Y1" s="45"/>
+      <c r="Z1" s="45"/>
+      <c r="AA1" s="45"/>
     </row>
     <row r="2" spans="1:27" ht="69.599999999999994" customHeight="1">
       <c r="A2" s="15" t="s">
@@ -13659,10 +13659,10 @@
       <c r="L2" s="23" t="s">
         <v>70</v>
       </c>
-      <c r="M2" s="44" t="s">
+      <c r="M2" s="40" t="s">
         <v>71</v>
       </c>
-      <c r="N2" s="44" t="s">
+      <c r="N2" s="40" t="s">
         <v>72</v>
       </c>
       <c r="O2" s="22" t="s">
@@ -13695,10 +13695,10 @@
       <c r="X2" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="Y2" s="45" t="s">
+      <c r="Y2" s="41" t="s">
         <v>83</v>
       </c>
-      <c r="Z2" s="45" t="s">
+      <c r="Z2" s="41" t="s">
         <v>84</v>
       </c>
       <c r="AA2" s="26" t="s">
@@ -13774,7 +13774,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:27" ht="19.149999999999999">
+    <row r="4" spans="1:27" ht="19.5">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -13843,7 +13843,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:27" ht="19.149999999999999">
+    <row r="5" spans="1:27" ht="19.5">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -13912,7 +13912,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="19.149999999999999">
+    <row r="6" spans="1:27" ht="19.5">
       <c r="A6" s="1">
         <v>1</v>
       </c>
@@ -13981,7 +13981,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="19.149999999999999">
+    <row r="7" spans="1:27" ht="19.5">
       <c r="A7" s="1">
         <v>1</v>
       </c>
@@ -14050,7 +14050,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="19.149999999999999">
+    <row r="8" spans="1:27" ht="19.5">
       <c r="A8" s="1">
         <v>1</v>
       </c>
@@ -14119,7 +14119,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="19.149999999999999">
+    <row r="9" spans="1:27" ht="19.5">
       <c r="A9" s="1">
         <v>1</v>
       </c>
@@ -14188,7 +14188,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="19.149999999999999">
+    <row r="10" spans="1:27" ht="19.5">
       <c r="A10" s="1">
         <v>1</v>
       </c>
@@ -14257,8 +14257,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:27" s="7" customFormat="1"/>
-    <row r="12" spans="1:27" ht="19.149999999999999">
+    <row r="11" spans="1:27" s="7" customFormat="1" ht="15"/>
+    <row r="12" spans="1:27" ht="38.25">
       <c r="A12" s="1">
         <v>2</v>
       </c>
@@ -14327,7 +14327,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:27" ht="19.149999999999999">
+    <row r="13" spans="1:27" ht="19.5">
       <c r="A13" s="1">
         <v>2</v>
       </c>
@@ -14396,7 +14396,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:27" ht="19.149999999999999">
+    <row r="14" spans="1:27" ht="19.5">
       <c r="A14" s="1">
         <v>2</v>
       </c>
@@ -14465,7 +14465,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="19.149999999999999">
+    <row r="15" spans="1:27" ht="19.5">
       <c r="A15" s="1">
         <v>2</v>
       </c>
@@ -14534,7 +14534,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="19.149999999999999">
+    <row r="16" spans="1:27" ht="19.5">
       <c r="A16" s="1">
         <v>2</v>
       </c>
@@ -14603,7 +14603,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="19.149999999999999">
+    <row r="17" spans="1:27" ht="19.5">
       <c r="A17" s="1">
         <v>2</v>
       </c>
@@ -14672,7 +14672,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="19.149999999999999">
+    <row r="18" spans="1:27" ht="19.5">
       <c r="A18" s="1">
         <v>2</v>
       </c>
@@ -14741,7 +14741,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="19.149999999999999">
+    <row r="19" spans="1:27" ht="19.5">
       <c r="A19" s="1">
         <v>2</v>
       </c>
@@ -14810,8 +14810,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:27" s="7" customFormat="1"/>
-    <row r="21" spans="1:27" ht="19.149999999999999">
+    <row r="20" spans="1:27" s="7" customFormat="1" ht="15"/>
+    <row r="21" spans="1:27" ht="38.25">
       <c r="A21" s="1">
         <v>3</v>
       </c>
@@ -14880,7 +14880,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:27" ht="19.149999999999999">
+    <row r="22" spans="1:27" ht="19.5">
       <c r="A22" s="1">
         <v>3</v>
       </c>
@@ -14949,7 +14949,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:27" ht="19.149999999999999">
+    <row r="23" spans="1:27" ht="19.5">
       <c r="A23" s="1">
         <v>3</v>
       </c>
@@ -15018,7 +15018,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:27" ht="19.149999999999999">
+    <row r="24" spans="1:27" ht="19.5">
       <c r="A24" s="1">
         <v>3</v>
       </c>
@@ -15087,7 +15087,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:27" ht="19.149999999999999">
+    <row r="25" spans="1:27" ht="19.5">
       <c r="A25" s="1">
         <v>3</v>
       </c>
@@ -15156,7 +15156,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:27" ht="19.149999999999999">
+    <row r="26" spans="1:27" ht="19.5">
       <c r="A26" s="1">
         <v>3</v>
       </c>
@@ -15225,7 +15225,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:27" ht="19.149999999999999">
+    <row r="27" spans="1:27" ht="19.5">
       <c r="A27" s="1">
         <v>3</v>
       </c>
@@ -15294,7 +15294,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:27" ht="19.149999999999999">
+    <row r="28" spans="1:27" ht="19.5">
       <c r="A28" s="1">
         <v>3</v>
       </c>
@@ -15363,7 +15363,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:27" ht="19.149999999999999">
+    <row r="29" spans="1:27" ht="19.5">
       <c r="A29" s="1">
         <v>3</v>
       </c>
@@ -15432,8 +15432,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:27" s="7" customFormat="1"/>
-    <row r="31" spans="1:27" ht="19.149999999999999">
+    <row r="30" spans="1:27" s="7" customFormat="1" ht="15"/>
+    <row r="31" spans="1:27" ht="19.5">
       <c r="A31" s="1">
         <v>4</v>
       </c>
@@ -15502,7 +15502,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:27" ht="19.149999999999999">
+    <row r="32" spans="1:27" ht="19.5">
       <c r="A32" s="1">
         <v>4</v>
       </c>
@@ -15571,7 +15571,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:27" ht="19.149999999999999">
+    <row r="33" spans="1:27" ht="19.5">
       <c r="A33" s="1">
         <v>4</v>
       </c>
@@ -15640,7 +15640,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:27" ht="19.149999999999999">
+    <row r="34" spans="1:27" ht="19.5">
       <c r="A34" s="1">
         <v>4</v>
       </c>
@@ -15709,7 +15709,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:27" ht="19.149999999999999">
+    <row r="35" spans="1:27" ht="38.25">
       <c r="A35" s="1">
         <v>4</v>
       </c>
@@ -15778,7 +15778,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:27" ht="19.149999999999999">
+    <row r="36" spans="1:27" ht="19.5">
       <c r="A36" s="1">
         <v>4</v>
       </c>
@@ -15847,7 +15847,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:27" ht="19.149999999999999">
+    <row r="37" spans="1:27" ht="19.5">
       <c r="A37" s="37">
         <v>4</v>
       </c>
@@ -15916,7 +15916,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:27" ht="19.149999999999999">
+    <row r="38" spans="1:27" ht="19.5">
       <c r="A38" s="1">
         <v>4</v>
       </c>
@@ -15985,7 +15985,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:27" ht="19.149999999999999">
+    <row r="39" spans="1:27" ht="19.5">
       <c r="A39" s="1">
         <v>4</v>
       </c>
@@ -16054,7 +16054,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:27" ht="19.149999999999999">
+    <row r="40" spans="1:27" ht="19.5">
       <c r="A40" s="37">
         <v>4</v>
       </c>
@@ -16123,7 +16123,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:27" ht="19.149999999999999">
+    <row r="41" spans="1:27" ht="19.5">
       <c r="A41" s="1">
         <v>4</v>
       </c>
@@ -16192,8 +16192,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:27" s="7" customFormat="1"/>
-    <row r="43" spans="1:27" ht="19.149999999999999">
+    <row r="42" spans="1:27" s="7" customFormat="1" ht="15"/>
+    <row r="43" spans="1:27" ht="19.5">
       <c r="A43" s="1">
         <v>5</v>
       </c>
@@ -16262,7 +16262,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:27" ht="19.149999999999999">
+    <row r="44" spans="1:27" ht="19.5">
       <c r="A44" s="1">
         <v>5</v>
       </c>
@@ -16331,7 +16331,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:27" ht="19.149999999999999">
+    <row r="45" spans="1:27" ht="19.5">
       <c r="A45" s="1">
         <v>5</v>
       </c>
@@ -16400,7 +16400,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:27" ht="19.149999999999999">
+    <row r="46" spans="1:27" ht="19.5">
       <c r="A46" s="1">
         <v>5</v>
       </c>
@@ -16469,7 +16469,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:27" ht="19.149999999999999">
+    <row r="47" spans="1:27" ht="38.25">
       <c r="A47" s="1">
         <v>5</v>
       </c>
@@ -16538,7 +16538,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:27" ht="19.149999999999999">
+    <row r="48" spans="1:27" ht="19.5">
       <c r="A48" s="1">
         <v>5</v>
       </c>
@@ -16607,7 +16607,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:27" ht="19.149999999999999">
+    <row r="49" spans="1:27" ht="19.5">
       <c r="A49" s="37">
         <v>5</v>
       </c>
@@ -16676,7 +16676,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:27" ht="19.149999999999999">
+    <row r="50" spans="1:27" ht="19.5">
       <c r="A50" s="1">
         <v>5</v>
       </c>
@@ -16745,7 +16745,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:27" ht="19.149999999999999">
+    <row r="51" spans="1:27" ht="19.5">
       <c r="A51" s="1">
         <v>5</v>
       </c>
@@ -16814,7 +16814,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:27" ht="19.149999999999999">
+    <row r="52" spans="1:27" ht="19.5">
       <c r="A52" s="37">
         <v>5</v>
       </c>
@@ -16883,7 +16883,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:27" ht="19.149999999999999">
+    <row r="53" spans="1:27" ht="19.5">
       <c r="A53" s="1">
         <v>5</v>
       </c>
@@ -16952,8 +16952,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:27" s="7" customFormat="1"/>
-    <row r="55" spans="1:27" ht="19.149999999999999">
+    <row r="54" spans="1:27" s="7" customFormat="1" ht="15"/>
+    <row r="55" spans="1:27" ht="19.5">
       <c r="A55" s="1">
         <v>6</v>
       </c>
@@ -17022,7 +17022,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:27" ht="19.149999999999999">
+    <row r="56" spans="1:27" ht="19.5">
       <c r="A56" s="1">
         <v>6</v>
       </c>
@@ -17091,7 +17091,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:27" ht="19.149999999999999">
+    <row r="57" spans="1:27" ht="19.5">
       <c r="A57" s="1">
         <v>6</v>
       </c>
@@ -17160,7 +17160,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:27" ht="19.149999999999999">
+    <row r="58" spans="1:27" ht="19.5">
       <c r="A58" s="1">
         <v>6</v>
       </c>
@@ -17229,7 +17229,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:27" ht="19.149999999999999">
+    <row r="59" spans="1:27" ht="38.25">
       <c r="A59" s="1">
         <v>6</v>
       </c>
@@ -17298,7 +17298,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:27" ht="19.149999999999999">
+    <row r="60" spans="1:27" ht="19.5">
       <c r="A60" s="1">
         <v>6</v>
       </c>
@@ -17367,7 +17367,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:27" ht="19.149999999999999">
+    <row r="61" spans="1:27" ht="19.5">
       <c r="A61" s="37">
         <v>6</v>
       </c>
@@ -17436,7 +17436,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:27" ht="19.149999999999999">
+    <row r="62" spans="1:27" ht="19.5">
       <c r="A62" s="1">
         <v>6</v>
       </c>
@@ -17505,7 +17505,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:27" ht="19.149999999999999">
+    <row r="63" spans="1:27" ht="19.5">
       <c r="A63" s="1">
         <v>6</v>
       </c>
@@ -17574,7 +17574,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:27" ht="19.149999999999999">
+    <row r="64" spans="1:27" ht="19.5">
       <c r="A64" s="37">
         <v>6</v>
       </c>
@@ -17643,7 +17643,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:27" ht="19.149999999999999">
+    <row r="65" spans="1:27" ht="19.5">
       <c r="A65" s="1">
         <v>6</v>
       </c>
@@ -17712,8 +17712,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:27" s="7" customFormat="1"/>
-    <row r="67" spans="1:27" ht="19.149999999999999">
+    <row r="66" spans="1:27" s="7" customFormat="1" ht="15"/>
+    <row r="67" spans="1:27" ht="19.5">
       <c r="A67" s="10">
         <v>7</v>
       </c>
@@ -17782,7 +17782,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:27" ht="19.149999999999999">
+    <row r="68" spans="1:27" ht="19.5">
       <c r="A68" s="10">
         <v>7</v>
       </c>
@@ -17851,7 +17851,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:27" ht="19.149999999999999">
+    <row r="69" spans="1:27" ht="19.5">
       <c r="A69" s="10">
         <v>7</v>
       </c>
@@ -17920,7 +17920,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:27" ht="19.149999999999999">
+    <row r="70" spans="1:27" ht="19.5">
       <c r="A70" s="10">
         <v>7</v>
       </c>
@@ -17989,7 +17989,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:27" ht="19.149999999999999">
+    <row r="71" spans="1:27" ht="38.25">
       <c r="A71" s="10">
         <v>7</v>
       </c>
@@ -18058,7 +18058,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:27" ht="19.149999999999999">
+    <row r="72" spans="1:27" ht="19.5">
       <c r="A72" s="10">
         <v>7</v>
       </c>
@@ -18127,7 +18127,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:27" ht="19.149999999999999">
+    <row r="73" spans="1:27" ht="19.5">
       <c r="A73" s="38">
         <v>7</v>
       </c>
@@ -18196,7 +18196,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:27" ht="19.149999999999999">
+    <row r="74" spans="1:27" ht="19.5">
       <c r="A74" s="10">
         <v>7</v>
       </c>
@@ -18265,7 +18265,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:27" ht="19.149999999999999">
+    <row r="75" spans="1:27" ht="19.5">
       <c r="A75" s="10">
         <v>7</v>
       </c>
@@ -18334,7 +18334,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:27" ht="19.149999999999999">
+    <row r="76" spans="1:27" ht="19.5">
       <c r="A76" s="38">
         <v>7</v>
       </c>
@@ -18403,7 +18403,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:27" ht="19.149999999999999">
+    <row r="77" spans="1:27" ht="19.5">
       <c r="A77" s="10">
         <v>7</v>
       </c>
@@ -18472,8 +18472,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:27" s="7" customFormat="1"/>
-    <row r="79" spans="1:27" ht="19.149999999999999">
+    <row r="78" spans="1:27" s="7" customFormat="1" ht="15"/>
+    <row r="79" spans="1:27" ht="19.5">
       <c r="A79" s="10">
         <v>8</v>
       </c>
@@ -18542,7 +18542,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:27" ht="19.149999999999999">
+    <row r="80" spans="1:27" ht="19.5">
       <c r="A80" s="10">
         <v>8</v>
       </c>
@@ -18611,7 +18611,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:27" ht="19.149999999999999">
+    <row r="81" spans="1:27" ht="19.5">
       <c r="A81" s="10">
         <v>8</v>
       </c>
@@ -18680,7 +18680,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:27" ht="19.149999999999999">
+    <row r="82" spans="1:27" ht="19.5">
       <c r="A82" s="10">
         <v>8</v>
       </c>
@@ -18749,7 +18749,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:27" ht="19.149999999999999">
+    <row r="83" spans="1:27" ht="19.5">
       <c r="A83" s="10">
         <v>8</v>
       </c>
@@ -18818,7 +18818,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:27" ht="19.149999999999999">
+    <row r="84" spans="1:27" ht="19.5">
       <c r="A84" s="10">
         <v>8</v>
       </c>
@@ -18887,7 +18887,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:27" ht="19.149999999999999">
+    <row r="85" spans="1:27" ht="19.5">
       <c r="A85" s="38">
         <v>8</v>
       </c>
@@ -18956,7 +18956,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:27" ht="19.149999999999999">
+    <row r="86" spans="1:27" ht="19.5">
       <c r="A86" s="10">
         <v>8</v>
       </c>
@@ -19025,7 +19025,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:27" ht="19.149999999999999">
+    <row r="87" spans="1:27" ht="19.5">
       <c r="A87" s="10">
         <v>8</v>
       </c>
@@ -19094,7 +19094,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:27" ht="19.149999999999999">
+    <row r="88" spans="1:27" ht="19.5">
       <c r="A88" s="38">
         <v>8</v>
       </c>
@@ -19163,7 +19163,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:27" ht="19.149999999999999">
+    <row r="89" spans="1:27" ht="19.5">
       <c r="A89" s="10">
         <v>8</v>
       </c>
@@ -19232,8 +19232,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:27" s="7" customFormat="1"/>
-    <row r="91" spans="1:27" ht="19.149999999999999">
+    <row r="90" spans="1:27" s="7" customFormat="1" ht="15"/>
+    <row r="91" spans="1:27" ht="19.5">
       <c r="A91" s="10">
         <v>9</v>
       </c>
@@ -19302,7 +19302,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:27" ht="19.149999999999999">
+    <row r="92" spans="1:27" ht="19.5">
       <c r="A92" s="10">
         <v>9</v>
       </c>
@@ -19371,7 +19371,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:27" ht="19.149999999999999">
+    <row r="93" spans="1:27" ht="19.5">
       <c r="A93" s="10">
         <v>9</v>
       </c>
@@ -19440,7 +19440,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:27" ht="19.149999999999999">
+    <row r="94" spans="1:27" ht="19.5">
       <c r="A94" s="10">
         <v>9</v>
       </c>
@@ -19509,7 +19509,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:27" ht="19.149999999999999">
+    <row r="95" spans="1:27" ht="19.5">
       <c r="A95" s="10">
         <v>9</v>
       </c>
@@ -19578,7 +19578,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:27" ht="19.149999999999999">
+    <row r="96" spans="1:27" ht="19.5">
       <c r="A96" s="10">
         <v>9</v>
       </c>
@@ -19647,7 +19647,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:27" ht="19.149999999999999">
+    <row r="97" spans="1:27" ht="19.5">
       <c r="A97" s="38">
         <v>9</v>
       </c>
@@ -19716,7 +19716,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:27" ht="19.149999999999999">
+    <row r="98" spans="1:27" ht="19.5">
       <c r="A98" s="10">
         <v>9</v>
       </c>
@@ -19785,7 +19785,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:27" ht="19.149999999999999">
+    <row r="99" spans="1:27" ht="19.5">
       <c r="A99" s="10">
         <v>9</v>
       </c>
@@ -19854,7 +19854,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:27" ht="19.149999999999999">
+    <row r="100" spans="1:27" ht="19.5">
       <c r="A100" s="38">
         <v>9</v>
       </c>
@@ -19923,7 +19923,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:27" ht="19.149999999999999">
+    <row r="101" spans="1:27" ht="19.5">
       <c r="A101" s="10">
         <v>9</v>
       </c>
@@ -19992,8 +19992,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:27" s="7" customFormat="1"/>
-    <row r="103" spans="1:27" ht="19.149999999999999">
+    <row r="102" spans="1:27" s="7" customFormat="1" ht="15"/>
+    <row r="103" spans="1:27" ht="19.5">
       <c r="A103" s="10">
         <v>10</v>
       </c>
@@ -20062,7 +20062,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:27" ht="19.149999999999999">
+    <row r="104" spans="1:27" ht="19.5">
       <c r="A104" s="10">
         <v>10</v>
       </c>
@@ -20131,7 +20131,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:27" ht="19.149999999999999">
+    <row r="105" spans="1:27" ht="19.5">
       <c r="A105" s="10">
         <v>10</v>
       </c>
@@ -20200,7 +20200,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:27" ht="19.149999999999999">
+    <row r="106" spans="1:27" ht="19.5">
       <c r="A106" s="10">
         <v>10</v>
       </c>
@@ -20269,7 +20269,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:27" ht="19.149999999999999">
+    <row r="107" spans="1:27" ht="19.5">
       <c r="A107" s="10">
         <v>10</v>
       </c>
@@ -20338,7 +20338,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:27" ht="19.149999999999999">
+    <row r="108" spans="1:27" ht="19.5">
       <c r="A108" s="10">
         <v>10</v>
       </c>
@@ -20407,7 +20407,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:27" ht="19.149999999999999">
+    <row r="109" spans="1:27" ht="19.5">
       <c r="A109" s="38">
         <v>10</v>
       </c>
@@ -20476,7 +20476,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:27" ht="19.149999999999999">
+    <row r="110" spans="1:27" ht="19.5">
       <c r="A110" s="10">
         <v>10</v>
       </c>
@@ -20545,7 +20545,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:27" ht="19.149999999999999">
+    <row r="111" spans="1:27" ht="19.5">
       <c r="A111" s="10">
         <v>10</v>
       </c>
@@ -20614,7 +20614,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:27" ht="19.149999999999999">
+    <row r="112" spans="1:27" ht="19.5">
       <c r="A112" s="38">
         <v>10</v>
       </c>
@@ -20683,7 +20683,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:28" ht="19.149999999999999">
+    <row r="113" spans="1:28" ht="19.5">
       <c r="A113" s="10">
         <v>10</v>
       </c>
@@ -20753,7 +20753,7 @@
       </c>
     </row>
     <row r="114" spans="1:28" s="7" customFormat="1"/>
-    <row r="115" spans="1:28" ht="38.450000000000003">
+    <row r="115" spans="1:28" ht="38.25">
       <c r="A115" s="1" t="s">
         <v>23</v>
       </c>
@@ -20812,7 +20812,7 @@
       </c>
       <c r="W115" s="5"/>
       <c r="X115" s="1"/>
-      <c r="Y115" s="5"/>
+      <c r="Y115" s="1"/>
       <c r="Z115" s="5">
         <f t="shared" si="18"/>
         <v>0</v>
@@ -20822,7 +20822,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:28" ht="19.149999999999999">
+    <row r="116" spans="1:28" ht="19.5">
       <c r="A116" s="1" t="s">
         <v>23</v>
       </c>
@@ -20891,7 +20891,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:28" ht="19.149999999999999">
+    <row r="117" spans="1:28" ht="19.5">
       <c r="A117" s="1" t="s">
         <v>23</v>
       </c>
@@ -20960,7 +20960,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:28" ht="19.149999999999999">
+    <row r="118" spans="1:28" ht="19.5">
       <c r="A118" s="1" t="s">
         <v>23</v>
       </c>
@@ -21029,7 +21029,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:28" ht="38.450000000000003">
+    <row r="119" spans="1:28" ht="38.25">
       <c r="A119" s="1" t="s">
         <v>23</v>
       </c>
@@ -21098,7 +21098,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:28" ht="19.149999999999999">
+    <row r="120" spans="1:28" ht="38.25">
       <c r="A120" s="1" t="s">
         <v>23</v>
       </c>
@@ -21167,7 +21167,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:28" ht="38.450000000000003">
+    <row r="121" spans="1:28" ht="57.75">
       <c r="A121" s="1" t="s">
         <v>23</v>
       </c>
@@ -21236,7 +21236,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:28" ht="38.450000000000003">
+    <row r="122" spans="1:28" ht="38.25">
       <c r="A122" s="1" t="s">
         <v>23</v>
       </c>
@@ -21999,8 +21999,8 @@
   </sheetData>
   <protectedRanges>
     <protectedRange sqref="C2:C10 C12:C19 C21:C29 C31:C41 C43:C53 C55:C65 C67:C77 C79:C89 C115:C122 C103:C113 C91:C101" name="Textbooks"/>
-    <protectedRange sqref="J2:L2 D2:F10 D12:F19 D21:F29 D31:F41 D43:F53 D55:F65 D67:F77 D79:F89 D91:F101 D115:F122 P2:R10 N3:O10 V2:X10 T3:U10 N12:R19 T12:X19 H3:L10 Z3:AA10 Z12:AA19 H12:L19 N21:R29 T21:X29 Z21:AA29 H21:L29 T31:X41 Z31:AA41 H31:L41 T43:X53 Z43:AA53 H43:L53 T55:X65 Z55:AA65 H55:L65 T67:X77 Z67:AA77 H67:L77 T79:X89 Z79:AA89 H79:L89 T91:X101 Z91:AA101 H91:L101 T103:X113 Z103:AA113 H103:L113 N115:R122 T115:X122 Z115:AA122 H115:L122 D103:F113 N31:R41 N43:R53 N55:R65 N67:R77 N79:R89 N91:R101 N103:R113" name="LAS"/>
-    <protectedRange sqref="G2:I2 M2:O2 S2:U2 Y2:AA2 G3:G10 M3:M10 S3:S10 Y3:Y10 Y12:Y19 G12:G19 M12:M19 S12:S19 Y21:Y29 G21:G29 M21:M29 S21:S29 Y31:Y41 G31:G41 M31:M41 S31:S41 Y43:Y53 G43:G53 M43:M53 S43:S53 Y55:Y65 G55:G65 M55:M65 S55:S65 Y67:Y77 G67:G77 M67:M77 S67:S77 Y79:Y89 G79:G89 M79:M89 S79:S89 Y91:Y101 G91:G101 M91:M101 S91:S101 Y103:Y113 G103:G113 M103:M113 S103:S113 Y115:Y122 G115:G122 M115:M122 S115:S122" name="SOURCE"/>
+    <protectedRange sqref="J2:L2 N3:O10 T3:U10 Z3:AA10 Z12:AA19 Z21:AA29 Z31:AA41 Z43:AA53 Z55:AA65 Z67:AA77 Z79:AA89 Z91:AA101 Z103:AA113 Z115:AA122 D2:F10 D12:F19 D21:F29 D31:F41 D43:F53 D55:F65 D67:F77 D103:F113 D79:F89 D91:F101 D115:F122 H3:L10 H67:L77 H103:L113 H12:L19 H21:L29 H31:L41 H43:L53 H55:L65 H79:L89 H91:L101 H115:L122 P2:R10 N67:R77 N103:R113 N12:R19 N21:R29 N31:R41 N43:R53 N55:R65 N79:R89 N91:R101 N115:R122 V2:X10 T67:X77 T103:X113 T12:X19 T21:X29 T31:X41 T43:X53 T55:X65 T79:X89 T91:X101 Y115 T115:X122" name="LAS"/>
+    <protectedRange sqref="G2:I2 M2:O2 S2:U2 Y2:AA2 G3:G10 M3:M10 S3:S10 Y3:Y10 Y12:Y19 G12:G19 M12:M19 S12:S19 Y21:Y29 G21:G29 M21:M29 S21:S29 Y31:Y41 G31:G41 M31:M41 S31:S41 Y43:Y53 G43:G53 M43:M53 S43:S53 Y55:Y65 G55:G65 M55:M65 S55:S65 Y67:Y77 G67:G77 M67:M77 S67:S77 Y79:Y89 G79:G89 M79:M89 S79:S89 Y91:Y101 G91:G101 M91:M101 S91:S101 Y103:Y113 G103:G113 M103:M113 S103:S113 Y116:Y122 G115:G122 M115:M122 S115:S122" name="SOURCE"/>
   </protectedRanges>
   <dataConsolidate/>
   <mergeCells count="4">
@@ -22009,12 +22009,15 @@
     <mergeCell ref="P1:U1"/>
     <mergeCell ref="V1:AA1"/>
   </mergeCells>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S115:S122 Y115:Y122 G115:G122 Y3:Y10 S3:S10 M3:M10 G3:G10 G12:G19 Y12:Y19 S12:S19 M12:M19 M21:M29 G21:G29 Y21:Y29 S21:S29 S31:S41 M31:M41 G31:G41 Y31:Y41 Y43:Y53 S43:S53 M43:M53 G43:G53 G55:G65 Y55:Y65 S55:S65 M55:M65 M67:M77 G67:G77 Y67:Y77 S67:S77 S79:S89 M79:M89 G79:G89 Y79:Y89 Y91:Y101 S91:S101 M91:M101 G91:G101 G103:G113 Y103:Y113 S103:S113 M103:M113 M115:M122" xr:uid="{CBD486C7-A5DB-48F1-B496-5027CC51E830}">
+  <dataValidations count="3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S115:S122 M115:M122 G115:G122 Y3:Y10 S3:S10 M3:M10 G3:G10 G12:G19 Y12:Y19 S12:S19 M12:M19 M21:M29 G21:G29 Y21:Y29 S21:S29 S31:S41 M31:M41 G31:G41 Y31:Y41 Y43:Y53 S43:S53 M43:M53 G43:G53 G55:G65 Y55:Y65 S55:S65 M55:M65 M67:M77 G67:G77 Y67:Y77 S67:S77 S79:S89 M79:M89 G79:G89 Y79:Y89 Y91:Y101 S91:S101 M91:M101 G91:G101 G103:G113 Y103:Y113 S103:S113 M103:M113 Y116:Y122" xr:uid="{CBD486C7-A5DB-48F1-B496-5027CC51E830}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X21:X29 X31:X41 X43:X53 X67:X77 X79:X89 X55:X65 X91:X101 X103:X113 X12:X19 X3:X10 L21:L29 L31:L41 L43:L53 L67:L77 L79:L89 L55:L65 L91:L101 L103:L113 L12:L19 L3:L10 R21:R29 R31:R41 R43:R53 R67:R77 R79:R89 R55:R65 R91:R101 R103:R113 R12:R19 R3:R10 F21:F29 F31:F41 F43:F53 F67:F77 F79:F89 F55:F65 F3:F10 F91:F101 X115:X122 F12:F19 F115:F122 R115:R122 L115:L122 F103:F113" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y115" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
       <formula1>"2024,2025"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F3:F10 F12:F19 F21:F29 F31:F41 F43:F53 F55:F65 F103:F113 F67:F77 F79:F89 F91:F101 F115:F122 L103:L113 L55:L65 L3:L10 L12:L19 L21:L29 L31:L41 L43:L53 L67:L77 L79:L89 L91:L101 L115:L122 R103:R113 R55:R65 R3:R10 R12:R19 R21:R29 R31:R41 R43:R53 R67:R77 R79:R89 R91:R101 R115:R122 X103:X113 X55:X65 X3:X10 X12:X19 X21:X29 X31:X41 X43:X53 X67:X77 X79:X89 X91:X101 X115:X122" xr:uid="{B0701DEB-6FF8-4596-B74A-027964A531F7}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
